--- a/firmware/Codigos Arduino/Planilha de Garras para produção.xlsx
+++ b/firmware/Codigos Arduino/Planilha de Garras para produção.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ramon Valverde\Desktop\Esteira-Automacao-Arduino-Codigos\Codigos Esteira Arduino\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ramon Valverde\Documents\Desenvolvedor\Sites\Sistema-de-Automacao-com-Visao-Computacional-e-IA\firmware\Codigos Arduino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C32721-C8C5-452B-929E-1BDAB2717EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6FCDD0-F357-4257-996B-456492D5C58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A45A9E4D-90FB-46DA-BA86-7690616B5799}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>Garrafa</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>Sprite com Fanta Uva</t>
+  </si>
+  <si>
+    <t>Feitas</t>
+  </si>
+  <si>
+    <t>✔️</t>
   </si>
 </sst>
 </file>
@@ -147,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -231,21 +237,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -334,13 +325,116 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -355,48 +449,80 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,192 +837,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA909FA8-5C01-4087-BC0B-F44FA329A385}">
-  <dimension ref="B1:D31"/>
+  <dimension ref="B1:H31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="8" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
+      <c r="E2" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="12">
         <v>4</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E3" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="4">
         <v>4</v>
       </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D4" s="14"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D5" s="14"/>
+      <c r="E5" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4">
         <v>4</v>
       </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D6" s="14"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="32"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="27"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="25" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
+    </row>
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D9" s="26"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="5"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D10" s="26"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="27"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D12" s="26"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+    </row>
+    <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
       </c>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D13" s="26"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
+    </row>
+    <row r="14" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D14" s="26"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="27"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
+    </row>
+    <row r="16" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="25" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="4">
         <v>1</v>
       </c>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D17" s="26"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
+    </row>
+    <row r="18" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
       </c>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="17"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="22"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="27"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="21"/>
-    </row>
-    <row r="20" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="25" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="9" t="s">
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
+    </row>
+    <row r="21" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="2:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="14" t="s">
+      <c r="D21" s="28"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="24"/>
+    </row>
+    <row r="22" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="15">
@@ -904,38 +1123,43 @@
         <v>25</v>
       </c>
       <c r="D22" s="16"/>
-    </row>
-    <row r="23" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
     </row>
-    <row r="27" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="28" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C22:D22"/>
+  <mergeCells count="2">
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="C22:H22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
